--- a/results/Rede4genes_Expressao_Datasets.xlsx
+++ b/results/Rede4genes_Expressao_Datasets.xlsx
@@ -59,7 +59,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+        <bgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -132,6 +138,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -946,60 +955,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Gene</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>O que a literatura diz (não HPA)</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Nível confirmado no HPA (screenshot da usuária, 28/08/2026)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>O que a literatura diz</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Implicação para POP/SUI</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>Link para conferir nível exato (HPA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Link para conferir (KREMEN1 ainda pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="220" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>CALML5</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Proteína ligante de cálcio específica de queratinócitos em diferenciação terminal, expressa em epitélio escamoso estratificado (originalmente descrita na epiderme). Página do HPA cataloga expressão em útero, vagina, endométrio e colo do útero, mas o nível exato não veio no resumo de busca.</t>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>CONFIRMADO por imuno-histoquímica (anticorpo HPA040725) e RNA (GTEx): Vagina - proteína Low (células epiteliais escamosas), RNA 272,7 nTPM. Cérvice - proteína Medium (células epiteliais escamosas; glandulares = Not detected), RNA 198,9 nTPM. Overview de proteína: Skin/Breast/Salivary gland = High; Cervix/Tonsil = Medium; Vagina/Oral mucosa = Low; resto do corpo = Not detected.</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Vagina/colo/ectocérvice SÃO epitélio escamoso estratificado (mesma família tecidual da pele) — biologicamente plausível que CALML5 seja expressa aí de forma real, reforçando a hipótese de cornificação/diferenciação epitelial alterada já discutida.</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
+          <t>Proteína ligante de cálcio de queratinócitos em diferenciação terminal, associada a TGM3 no envelope cornificado (já citado no rascunho da usuária).</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Expressão real, substancial e ESPECÍFICA de células epiteliais escamosas (não glandulares) em vagina e cérvice humanas — exatamente o tipo celular da hipótese de cornificação/diferenciação epitelial. Isso NÃO prova que CALML5 muda entre POP/SUI e controle (é expressão basal em tecido saudável do GTEx, não comparação de doença) — mas resolve a dúvida de fundo: CALML5 não é um gene obscuro/mal expresso nesse tipo de tecido, é um gene real e robustamente expresso lá. Isso enfraquece (não elimina) a preocupação de falso positivo técnico no rato: o padrão 0 nas 3 Untreated / valores altos em 2 das 3 Treated é mais compatível com indução biológica real (liga/desliga) do que com o gene simplesmente "não existir" nesse tecido. A limitação estatística de n=3 por grupo no rato continua de pé — isso é sobre poder amostral, não sobre se o gene é real.</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>https://www.proteinatlas.org/ENSG00000178372-CALML5/tissue</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="90" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>KREMEN1</t>
@@ -1007,15 +1027,20 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Receptor transmembrana que forma complexo com DKK1 e LRP5/LRP6, regulador central da via Wnt/beta-catenina (inibe endocitando os correceptores LRP5/6). HPA cataloga expressão em cérvice (ecto e endocérvice), tuba uterina, ovário, útero e vagina.</t>
+          <t>AINDA NÃO CONFERIDO — mesma checagem que você fez para CALML5, faça para KREMEN1 na mesma página (Tissue &gt; Vagina / Cervix / Uterus) e me manda print se quiser que eu documente aqui também.</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Via Wnt é conhecida por regular renovação/diferenciação epitelial e remodelação de tecido conjuntivo — plausível biologicamente que KREMEN1 alterado contribua tanto para a via epitelial (POP) quanto para reparo tecidual após lesão (SUI), mas isso é inferência de mecanismo geral, não medição direta no tecido pélvico.</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
+          <t>Receptor transmembrana que forma complexo com DKK1 e LRP5/LRP6, regulador central da via Wnt/beta-catenina (inibe endocitando os correceptores LRP5/6).</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Via Wnt regula renovação/diferenciação epitelial e remodelação de tecido conjuntivo — plausível para POP (passivo) e SUI (reparo pós-lesão), mas ainda é inferência de mecanismo geral até você confirmar o nível real no HPA.</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>https://www.proteinatlas.org/ENSG00000183762-KREMEN1/tissue</t>
         </is>
@@ -1024,7 +1049,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
